--- a/alligator_data.xlsx
+++ b/alligator_data.xlsx
@@ -1,84 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MillionsKeeper\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Дата</t>
-  </si>
-  <si>
-    <t>Событие</t>
-  </si>
-  <si>
-    <t>Пара</t>
-  </si>
-  <si>
-    <t>Челюсть (Jaw)</t>
-  </si>
-  <si>
-    <t>Зубы (Teeth)</t>
-  </si>
-  <si>
-    <t>Губы (Lips)</t>
-  </si>
-  <si>
-    <t>Угол</t>
-  </si>
-  <si>
-    <t>Разница со свечой</t>
-  </si>
-  <si>
-    <t>Разница Lips/Teeth</t>
-  </si>
-  <si>
-    <t>Комментарий</t>
-  </si>
-  <si>
-    <t>2025-06-03 22:42:17</t>
-  </si>
-  <si>
-    <t>OPEN_LONG</t>
-  </si>
-  <si>
-    <t>EURCHFrfd</t>
-  </si>
-  <si>
-    <t>Ордер LONG выставлен по условию</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -97,24 +46,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -402,84 +410,356 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="1"/>
-    <col min="8" max="8" width="25.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="55.42578125" style="1" customWidth="1"/>
+    <col width="21.5703125" customWidth="1" style="1" min="1" max="1"/>
+    <col width="18.140625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="17.140625" customWidth="1" style="1" min="3" max="3"/>
+    <col width="21.5703125" customWidth="1" style="1" min="4" max="4"/>
+    <col width="16.28515625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="14.7109375" customWidth="1" style="1" min="6" max="6"/>
+    <col width="9.140625" customWidth="1" style="1" min="7" max="7"/>
+    <col width="25.140625" customWidth="1" style="1" min="8" max="8"/>
+    <col width="21.7109375" customWidth="1" style="1" min="9" max="9"/>
+    <col width="55.42578125" customWidth="1" style="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Событие</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Пара</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Челюсть (Jaw)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Зубы (Teeth)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Губы (Lips)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Угол</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Разница со свечой</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Разница Lips/Teeth</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-03 22:42:17</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>0.93509</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>0.93585</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>0.93652</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-06-04 06:47:14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.60039</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.60004</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-06-04 06:47:48</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>143.522</v>
+      </c>
+      <c r="E4" t="n">
+        <v>143.746</v>
+      </c>
+      <c r="F4" t="n">
+        <v>143.886</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>199</v>
+      </c>
+      <c r="I4" t="n">
+        <v>140</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-06-04 06:47:51</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CLOSE_SHORT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.85521</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.85486</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.85487</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>46</v>
+      </c>
+      <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Ордер SHORT снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-06-04 06:47:52</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.85521</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.85486</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.85487</v>
+      </c>
+      <c r="G6" t="n">
         <v>9</v>
       </c>
+      <c r="H6" t="n">
+        <v>46</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.93508999999999998</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.93584999999999996</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0.93652000000000002</v>
-      </c>
-      <c r="G2" s="1">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1">
-        <v>38</v>
-      </c>
-      <c r="I2" s="1">
-        <v>67</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-06-04 06:47:53</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3354.58</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3355.01</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3358.43</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>104</v>
+      </c>
+      <c r="I7" t="n">
+        <v>342</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-06-04 06:51:41</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.28814</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.28864</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.28911</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>118</v>
+      </c>
+      <c r="I8" t="n">
+        <v>47</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/alligator_data.xlsx
+++ b/alligator_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J431"/>
+  <dimension ref="A1:J669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.5703125" customWidth="1" style="1" min="1" max="1"/>
@@ -16031,7 +16031,8612 @@
       <c r="I431" t="n">
         <v>140</v>
       </c>
-      <c r="J431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2025-06-05 00:01:14</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>1.13939</v>
+      </c>
+      <c r="E432" t="n">
+        <v>1.14042</v>
+      </c>
+      <c r="F432" t="n">
+        <v>1.14137</v>
+      </c>
+      <c r="G432" t="n">
+        <v>6</v>
+      </c>
+      <c r="H432" t="n">
+        <v>59</v>
+      </c>
+      <c r="I432" t="n">
+        <v>95</v>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2025-06-05 00:01:42</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>1.13939</v>
+      </c>
+      <c r="E433" t="n">
+        <v>1.14042</v>
+      </c>
+      <c r="F433" t="n">
+        <v>1.14137</v>
+      </c>
+      <c r="G433" t="n">
+        <v>6</v>
+      </c>
+      <c r="H433" t="n">
+        <v>59</v>
+      </c>
+      <c r="I433" t="n">
+        <v>95</v>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2025-06-05 00:05:32</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>1.13939</v>
+      </c>
+      <c r="E434" t="n">
+        <v>1.14042</v>
+      </c>
+      <c r="F434" t="n">
+        <v>1.14137</v>
+      </c>
+      <c r="G434" t="n">
+        <v>6</v>
+      </c>
+      <c r="H434" t="n">
+        <v>59</v>
+      </c>
+      <c r="I434" t="n">
+        <v>95</v>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:33</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>1.13986</v>
+      </c>
+      <c r="E435" t="n">
+        <v>1.1407</v>
+      </c>
+      <c r="F435" t="n">
+        <v>1.14145</v>
+      </c>
+      <c r="G435" t="n">
+        <v>6</v>
+      </c>
+      <c r="H435" t="n">
+        <v>36</v>
+      </c>
+      <c r="I435" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:34</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>1.13986</v>
+      </c>
+      <c r="E436" t="n">
+        <v>1.1407</v>
+      </c>
+      <c r="F436" t="n">
+        <v>1.14145</v>
+      </c>
+      <c r="G436" t="n">
+        <v>6</v>
+      </c>
+      <c r="H436" t="n">
+        <v>36</v>
+      </c>
+      <c r="I436" t="n">
+        <v>75</v>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:35</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>0.60132</v>
+      </c>
+      <c r="E437" t="n">
+        <v>0.60207</v>
+      </c>
+      <c r="F437" t="n">
+        <v>0.60265</v>
+      </c>
+      <c r="G437" t="n">
+        <v>3</v>
+      </c>
+      <c r="H437" t="n">
+        <v>12</v>
+      </c>
+      <c r="I437" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:35</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>0.84189</v>
+      </c>
+      <c r="E438" t="n">
+        <v>0.84196</v>
+      </c>
+      <c r="F438" t="n">
+        <v>0.84211</v>
+      </c>
+      <c r="G438" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H438" t="n">
+        <v>18</v>
+      </c>
+      <c r="I438" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:36</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>0.82107</v>
+      </c>
+      <c r="E439" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F439" t="n">
+        <v>0.81872</v>
+      </c>
+      <c r="G439" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H439" t="n">
+        <v>45</v>
+      </c>
+      <c r="I439" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:37</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>0.82107</v>
+      </c>
+      <c r="E440" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F440" t="n">
+        <v>0.81872</v>
+      </c>
+      <c r="G440" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H440" t="n">
+        <v>45</v>
+      </c>
+      <c r="I440" t="n">
+        <v>128</v>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:37</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>143.529</v>
+      </c>
+      <c r="E441" t="n">
+        <v>143.287</v>
+      </c>
+      <c r="F441" t="n">
+        <v>142.964</v>
+      </c>
+      <c r="G441" t="n">
+        <v>-23</v>
+      </c>
+      <c r="H441" t="n">
+        <v>182</v>
+      </c>
+      <c r="I441" t="n">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:38</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>0.93616</v>
+      </c>
+      <c r="E442" t="n">
+        <v>0.9356100000000001</v>
+      </c>
+      <c r="F442" t="n">
+        <v>0.93484</v>
+      </c>
+      <c r="G442" t="n">
+        <v>-19</v>
+      </c>
+      <c r="H442" t="n">
+        <v>64</v>
+      </c>
+      <c r="I442" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:38</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>1.35371</v>
+      </c>
+      <c r="E443" t="n">
+        <v>1.35456</v>
+      </c>
+      <c r="F443" t="n">
+        <v>1.35504</v>
+      </c>
+      <c r="G443" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H443" t="n">
+        <v>6</v>
+      </c>
+      <c r="I443" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:39</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>1.36991</v>
+      </c>
+      <c r="E444" t="n">
+        <v>1.36862</v>
+      </c>
+      <c r="F444" t="n">
+        <v>1.36763</v>
+      </c>
+      <c r="G444" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H444" t="n">
+        <v>9</v>
+      </c>
+      <c r="I444" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:39</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>163.652</v>
+      </c>
+      <c r="E445" t="n">
+        <v>163.509</v>
+      </c>
+      <c r="F445" t="n">
+        <v>163.244</v>
+      </c>
+      <c r="G445" t="n">
+        <v>-29</v>
+      </c>
+      <c r="H445" t="n">
+        <v>234</v>
+      </c>
+      <c r="I445" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:40</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>0.88757</v>
+      </c>
+      <c r="E446" t="n">
+        <v>0.88785</v>
+      </c>
+      <c r="F446" t="n">
+        <v>0.8878200000000001</v>
+      </c>
+      <c r="G446" t="n">
+        <v>-23</v>
+      </c>
+      <c r="H446" t="n">
+        <v>91</v>
+      </c>
+      <c r="I446" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:40</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>CLOSE_LONG</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>0.88757</v>
+      </c>
+      <c r="E447" t="n">
+        <v>0.88785</v>
+      </c>
+      <c r="F447" t="n">
+        <v>0.8878200000000001</v>
+      </c>
+      <c r="G447" t="n">
+        <v>-23</v>
+      </c>
+      <c r="H447" t="n">
+        <v>91</v>
+      </c>
+      <c r="I447" t="n">
+        <v>3</v>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>Ордер LONG снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:40</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>0.88757</v>
+      </c>
+      <c r="E448" t="n">
+        <v>0.88785</v>
+      </c>
+      <c r="F448" t="n">
+        <v>0.8878200000000001</v>
+      </c>
+      <c r="G448" t="n">
+        <v>-23</v>
+      </c>
+      <c r="H448" t="n">
+        <v>91</v>
+      </c>
+      <c r="I448" t="n">
+        <v>3</v>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:41</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>0.6477000000000001</v>
+      </c>
+      <c r="E449" t="n">
+        <v>0.64861</v>
+      </c>
+      <c r="F449" t="n">
+        <v>0.6491400000000001</v>
+      </c>
+      <c r="G449" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H449" t="n">
+        <v>9</v>
+      </c>
+      <c r="I449" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:41</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>93.008</v>
+      </c>
+      <c r="E450" t="n">
+        <v>92.98399999999999</v>
+      </c>
+      <c r="F450" t="n">
+        <v>92.83199999999999</v>
+      </c>
+      <c r="G450" t="n">
+        <v>-40</v>
+      </c>
+      <c r="H450" t="n">
+        <v>203</v>
+      </c>
+      <c r="I450" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:42</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>0.53199</v>
+      </c>
+      <c r="E451" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="F451" t="n">
+        <v>0.53156</v>
+      </c>
+      <c r="G451" t="n">
+        <v>-26</v>
+      </c>
+      <c r="H451" t="n">
+        <v>62</v>
+      </c>
+      <c r="I451" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:42</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>174.789</v>
+      </c>
+      <c r="E452" t="n">
+        <v>174.743</v>
+      </c>
+      <c r="F452" t="n">
+        <v>174.574</v>
+      </c>
+      <c r="G452" t="n">
+        <v>-37</v>
+      </c>
+      <c r="H452" t="n">
+        <v>196</v>
+      </c>
+      <c r="I452" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:42</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>1.75917</v>
+      </c>
+      <c r="E453" t="n">
+        <v>1.75811</v>
+      </c>
+      <c r="F453" t="n">
+        <v>1.75781</v>
+      </c>
+      <c r="G453" t="n">
+        <v>6</v>
+      </c>
+      <c r="H453" t="n">
+        <v>81</v>
+      </c>
+      <c r="I453" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:43</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>1.11177</v>
+      </c>
+      <c r="E454" t="n">
+        <v>1.11103</v>
+      </c>
+      <c r="F454" t="n">
+        <v>1.10961</v>
+      </c>
+      <c r="G454" t="n">
+        <v>-31</v>
+      </c>
+      <c r="H454" t="n">
+        <v>112</v>
+      </c>
+      <c r="I454" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:43</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>1.56151</v>
+      </c>
+      <c r="E455" t="n">
+        <v>1.56106</v>
+      </c>
+      <c r="F455" t="n">
+        <v>1.56092</v>
+      </c>
+      <c r="G455" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H455" t="n">
+        <v>28</v>
+      </c>
+      <c r="I455" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:44</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>1.8546</v>
+      </c>
+      <c r="E456" t="n">
+        <v>1.85393</v>
+      </c>
+      <c r="F456" t="n">
+        <v>1.85324</v>
+      </c>
+      <c r="G456" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H456" t="n">
+        <v>56</v>
+      </c>
+      <c r="I456" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:44</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>3360.55</v>
+      </c>
+      <c r="E457" t="n">
+        <v>3366.04</v>
+      </c>
+      <c r="F457" t="n">
+        <v>3370.51</v>
+      </c>
+      <c r="G457" t="n">
+        <v>3</v>
+      </c>
+      <c r="H457" t="n">
+        <v>354</v>
+      </c>
+      <c r="I457" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:44</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>194.355</v>
+      </c>
+      <c r="E458" t="n">
+        <v>194.171</v>
+      </c>
+      <c r="F458" t="n">
+        <v>193.8</v>
+      </c>
+      <c r="G458" t="n">
+        <v>-42</v>
+      </c>
+      <c r="H458" t="n">
+        <v>349</v>
+      </c>
+      <c r="I458" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:45</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>34.4169</v>
+      </c>
+      <c r="E459" t="n">
+        <v>34.4489</v>
+      </c>
+      <c r="F459" t="n">
+        <v>34.4694</v>
+      </c>
+      <c r="G459" t="n">
+        <v>8</v>
+      </c>
+      <c r="H459" t="n">
+        <v>556</v>
+      </c>
+      <c r="I459" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:45</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="E460" t="n">
+        <v>1.28717</v>
+      </c>
+      <c r="F460" t="n">
+        <v>1.28627</v>
+      </c>
+      <c r="G460" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H460" t="n">
+        <v>68</v>
+      </c>
+      <c r="I460" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2025-06-05 01:05:46</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="E461" t="n">
+        <v>1.28717</v>
+      </c>
+      <c r="F461" t="n">
+        <v>1.28627</v>
+      </c>
+      <c r="G461" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H461" t="n">
+        <v>68</v>
+      </c>
+      <c r="I461" t="n">
+        <v>90</v>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:46</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E462" t="n">
+        <v>1.1408</v>
+      </c>
+      <c r="F462" t="n">
+        <v>1.14158</v>
+      </c>
+      <c r="G462" t="n">
+        <v>11</v>
+      </c>
+      <c r="H462" t="n">
+        <v>36</v>
+      </c>
+      <c r="I462" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:47</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>0.6014699999999999</v>
+      </c>
+      <c r="E463" t="n">
+        <v>0.60216</v>
+      </c>
+      <c r="F463" t="n">
+        <v>0.60261</v>
+      </c>
+      <c r="G463" t="n">
+        <v>0</v>
+      </c>
+      <c r="H463" t="n">
+        <v>15</v>
+      </c>
+      <c r="I463" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:47</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>0.84196</v>
+      </c>
+      <c r="E464" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F464" t="n">
+        <v>0.84228</v>
+      </c>
+      <c r="G464" t="n">
+        <v>10</v>
+      </c>
+      <c r="H464" t="n">
+        <v>30</v>
+      </c>
+      <c r="I464" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:47</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>0.82086</v>
+      </c>
+      <c r="E465" t="n">
+        <v>0.81975</v>
+      </c>
+      <c r="F465" t="n">
+        <v>0.81864</v>
+      </c>
+      <c r="G465" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H465" t="n">
+        <v>41</v>
+      </c>
+      <c r="I465" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:48</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>143.477</v>
+      </c>
+      <c r="E466" t="n">
+        <v>143.219</v>
+      </c>
+      <c r="F466" t="n">
+        <v>142.923</v>
+      </c>
+      <c r="G466" t="n">
+        <v>-19</v>
+      </c>
+      <c r="H466" t="n">
+        <v>165</v>
+      </c>
+      <c r="I466" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:48</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>0.93586</v>
+      </c>
+      <c r="E467" t="n">
+        <v>0.93531</v>
+      </c>
+      <c r="F467" t="n">
+        <v>0.93472</v>
+      </c>
+      <c r="G467" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H467" t="n">
+        <v>20</v>
+      </c>
+      <c r="I467" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:49</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>1.35382</v>
+      </c>
+      <c r="E468" t="n">
+        <v>1.35461</v>
+      </c>
+      <c r="F468" t="n">
+        <v>1.35505</v>
+      </c>
+      <c r="G468" t="n">
+        <v>0</v>
+      </c>
+      <c r="H468" t="n">
+        <v>2</v>
+      </c>
+      <c r="I468" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:49</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>1.36969</v>
+      </c>
+      <c r="E469" t="n">
+        <v>1.36846</v>
+      </c>
+      <c r="F469" t="n">
+        <v>1.36762</v>
+      </c>
+      <c r="G469" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H469" t="n">
+        <v>32</v>
+      </c>
+      <c r="I469" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:50</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>163.569</v>
+      </c>
+      <c r="E470" t="n">
+        <v>163.391</v>
+      </c>
+      <c r="F470" t="n">
+        <v>163.169</v>
+      </c>
+      <c r="G470" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H470" t="n">
+        <v>137</v>
+      </c>
+      <c r="I470" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:50</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>0.88763</v>
+      </c>
+      <c r="E471" t="n">
+        <v>0.88776</v>
+      </c>
+      <c r="F471" t="n">
+        <v>0.88775</v>
+      </c>
+      <c r="G471" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H471" t="n">
+        <v>29</v>
+      </c>
+      <c r="I471" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:50</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>0.64788</v>
+      </c>
+      <c r="E472" t="n">
+        <v>0.64868</v>
+      </c>
+      <c r="F472" t="n">
+        <v>0.64911</v>
+      </c>
+      <c r="G472" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H472" t="n">
+        <v>6</v>
+      </c>
+      <c r="I472" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:51</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>92.992</v>
+      </c>
+      <c r="E473" t="n">
+        <v>92.952</v>
+      </c>
+      <c r="F473" t="n">
+        <v>92.804</v>
+      </c>
+      <c r="G473" t="n">
+        <v>-22</v>
+      </c>
+      <c r="H473" t="n">
+        <v>139</v>
+      </c>
+      <c r="I473" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:51</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>0.5319199999999999</v>
+      </c>
+      <c r="E474" t="n">
+        <v>0.53177</v>
+      </c>
+      <c r="F474" t="n">
+        <v>0.53141</v>
+      </c>
+      <c r="G474" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H474" t="n">
+        <v>30</v>
+      </c>
+      <c r="I474" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:52</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>174.756</v>
+      </c>
+      <c r="E475" t="n">
+        <v>174.654</v>
+      </c>
+      <c r="F475" t="n">
+        <v>174.519</v>
+      </c>
+      <c r="G475" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H475" t="n">
+        <v>99</v>
+      </c>
+      <c r="I475" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:52</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>1.75887</v>
+      </c>
+      <c r="E476" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="F476" t="n">
+        <v>1.75814</v>
+      </c>
+      <c r="G476" t="n">
+        <v>11</v>
+      </c>
+      <c r="H476" t="n">
+        <v>73</v>
+      </c>
+      <c r="I476" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:54</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>CLOSE_SHORT</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>1.75887</v>
+      </c>
+      <c r="E477" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="F477" t="n">
+        <v>1.75814</v>
+      </c>
+      <c r="G477" t="n">
+        <v>11</v>
+      </c>
+      <c r="H477" t="n">
+        <v>73</v>
+      </c>
+      <c r="I477" t="n">
+        <v>4</v>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>Ордер SHORT снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:55</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>1.75887</v>
+      </c>
+      <c r="E478" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="F478" t="n">
+        <v>1.75814</v>
+      </c>
+      <c r="G478" t="n">
+        <v>11</v>
+      </c>
+      <c r="H478" t="n">
+        <v>73</v>
+      </c>
+      <c r="I478" t="n">
+        <v>4</v>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:55</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>1.11132</v>
+      </c>
+      <c r="E479" t="n">
+        <v>1.11042</v>
+      </c>
+      <c r="F479" t="n">
+        <v>1.1093</v>
+      </c>
+      <c r="G479" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H479" t="n">
+        <v>55</v>
+      </c>
+      <c r="I479" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:56</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>1.56137</v>
+      </c>
+      <c r="E480" t="n">
+        <v>1.56101</v>
+      </c>
+      <c r="F480" t="n">
+        <v>1.56107</v>
+      </c>
+      <c r="G480" t="n">
+        <v>4</v>
+      </c>
+      <c r="H480" t="n">
+        <v>5</v>
+      </c>
+      <c r="I480" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:56</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>1.85444</v>
+      </c>
+      <c r="E481" t="n">
+        <v>1.85381</v>
+      </c>
+      <c r="F481" t="n">
+        <v>1.85313</v>
+      </c>
+      <c r="G481" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H481" t="n">
+        <v>60</v>
+      </c>
+      <c r="I481" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:57</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>3361.89</v>
+      </c>
+      <c r="E482" t="n">
+        <v>3366.87</v>
+      </c>
+      <c r="F482" t="n">
+        <v>3371.13</v>
+      </c>
+      <c r="G482" t="n">
+        <v>5</v>
+      </c>
+      <c r="H482" t="n">
+        <v>206</v>
+      </c>
+      <c r="I482" t="n">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:57</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>194.241</v>
+      </c>
+      <c r="E483" t="n">
+        <v>194.007</v>
+      </c>
+      <c r="F483" t="n">
+        <v>193.675</v>
+      </c>
+      <c r="G483" t="n">
+        <v>-31</v>
+      </c>
+      <c r="H483" t="n">
+        <v>227</v>
+      </c>
+      <c r="I483" t="n">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:58</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>34.423</v>
+      </c>
+      <c r="E484" t="n">
+        <v>34.4544</v>
+      </c>
+      <c r="F484" t="n">
+        <v>34.473</v>
+      </c>
+      <c r="G484" t="n">
+        <v>3</v>
+      </c>
+      <c r="H484" t="n">
+        <v>90</v>
+      </c>
+      <c r="I484" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:58</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>1.2878</v>
+      </c>
+      <c r="E485" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="F485" t="n">
+        <v>1.28605</v>
+      </c>
+      <c r="G485" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H485" t="n">
+        <v>62</v>
+      </c>
+      <c r="I485" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2025-06-05 02:05:59</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>1.2878</v>
+      </c>
+      <c r="E486" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="F486" t="n">
+        <v>1.28605</v>
+      </c>
+      <c r="G486" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H486" t="n">
+        <v>62</v>
+      </c>
+      <c r="I486" t="n">
+        <v>95</v>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:05:59</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>1.14012</v>
+      </c>
+      <c r="E487" t="n">
+        <v>1.14093</v>
+      </c>
+      <c r="F487" t="n">
+        <v>1.14168</v>
+      </c>
+      <c r="G487" t="n">
+        <v>5</v>
+      </c>
+      <c r="H487" t="n">
+        <v>8</v>
+      </c>
+      <c r="I487" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:00</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>0.60159</v>
+      </c>
+      <c r="E488" t="n">
+        <v>0.60221</v>
+      </c>
+      <c r="F488" t="n">
+        <v>0.60268</v>
+      </c>
+      <c r="G488" t="n">
+        <v>5</v>
+      </c>
+      <c r="H488" t="n">
+        <v>13</v>
+      </c>
+      <c r="I488" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:00</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>0.84199</v>
+      </c>
+      <c r="E489" t="n">
+        <v>0.84207</v>
+      </c>
+      <c r="F489" t="n">
+        <v>0.84236</v>
+      </c>
+      <c r="G489" t="n">
+        <v>9</v>
+      </c>
+      <c r="H489" t="n">
+        <v>27</v>
+      </c>
+      <c r="I489" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:01</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>0.82067</v>
+      </c>
+      <c r="E490" t="n">
+        <v>0.81956</v>
+      </c>
+      <c r="F490" t="n">
+        <v>0.81848</v>
+      </c>
+      <c r="G490" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H490" t="n">
+        <v>21</v>
+      </c>
+      <c r="I490" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:01</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>143.426</v>
+      </c>
+      <c r="E491" t="n">
+        <v>143.163</v>
+      </c>
+      <c r="F491" t="n">
+        <v>142.874</v>
+      </c>
+      <c r="G491" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H491" t="n">
+        <v>80</v>
+      </c>
+      <c r="I491" t="n">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:01</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>0.93576</v>
+      </c>
+      <c r="E492" t="n">
+        <v>0.9352200000000001</v>
+      </c>
+      <c r="F492" t="n">
+        <v>0.93463</v>
+      </c>
+      <c r="G492" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H492" t="n">
+        <v>20</v>
+      </c>
+      <c r="I492" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:02</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>1.35391</v>
+      </c>
+      <c r="E493" t="n">
+        <v>1.35465</v>
+      </c>
+      <c r="F493" t="n">
+        <v>1.35504</v>
+      </c>
+      <c r="G493" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H493" t="n">
+        <v>31</v>
+      </c>
+      <c r="I493" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:02</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>1.36955</v>
+      </c>
+      <c r="E494" t="n">
+        <v>1.36833</v>
+      </c>
+      <c r="F494" t="n">
+        <v>1.36767</v>
+      </c>
+      <c r="G494" t="n">
+        <v>2</v>
+      </c>
+      <c r="H494" t="n">
+        <v>2</v>
+      </c>
+      <c r="I494" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:03</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>163.53</v>
+      </c>
+      <c r="E495" t="n">
+        <v>163.348</v>
+      </c>
+      <c r="F495" t="n">
+        <v>163.129</v>
+      </c>
+      <c r="G495" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H495" t="n">
+        <v>77</v>
+      </c>
+      <c r="I495" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:03</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>0.88766</v>
+      </c>
+      <c r="E496" t="n">
+        <v>0.88774</v>
+      </c>
+      <c r="F496" t="n">
+        <v>0.88773</v>
+      </c>
+      <c r="G496" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H496" t="n">
+        <v>2</v>
+      </c>
+      <c r="I496" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:04</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="E497" t="n">
+        <v>0.64871</v>
+      </c>
+      <c r="F497" t="n">
+        <v>0.64912</v>
+      </c>
+      <c r="G497" t="n">
+        <v>1</v>
+      </c>
+      <c r="H497" t="n">
+        <v>3</v>
+      </c>
+      <c r="I497" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:04</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>92.976</v>
+      </c>
+      <c r="E498" t="n">
+        <v>92.907</v>
+      </c>
+      <c r="F498" t="n">
+        <v>92.76600000000001</v>
+      </c>
+      <c r="G498" t="n">
+        <v>-26</v>
+      </c>
+      <c r="H498" t="n">
+        <v>72</v>
+      </c>
+      <c r="I498" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:05</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>0.53188</v>
+      </c>
+      <c r="E499" t="n">
+        <v>0.5317</v>
+      </c>
+      <c r="F499" t="n">
+        <v>0.5313</v>
+      </c>
+      <c r="G499" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H499" t="n">
+        <v>12</v>
+      </c>
+      <c r="I499" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:05</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>174.735</v>
+      </c>
+      <c r="E500" t="n">
+        <v>174.623</v>
+      </c>
+      <c r="F500" t="n">
+        <v>174.497</v>
+      </c>
+      <c r="G500" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H500" t="n">
+        <v>42</v>
+      </c>
+      <c r="I500" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:06</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>1.7588</v>
+      </c>
+      <c r="E501" t="n">
+        <v>1.75816</v>
+      </c>
+      <c r="F501" t="n">
+        <v>1.75838</v>
+      </c>
+      <c r="G501" t="n">
+        <v>10</v>
+      </c>
+      <c r="H501" t="n">
+        <v>6</v>
+      </c>
+      <c r="I501" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:06</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>1.11114</v>
+      </c>
+      <c r="E502" t="n">
+        <v>1.11023</v>
+      </c>
+      <c r="F502" t="n">
+        <v>1.1091</v>
+      </c>
+      <c r="G502" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H502" t="n">
+        <v>53</v>
+      </c>
+      <c r="I502" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:06</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>1.56136</v>
+      </c>
+      <c r="E503" t="n">
+        <v>1.56104</v>
+      </c>
+      <c r="F503" t="n">
+        <v>1.56122</v>
+      </c>
+      <c r="G503" t="n">
+        <v>6</v>
+      </c>
+      <c r="H503" t="n">
+        <v>9</v>
+      </c>
+      <c r="I503" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:08</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>CLOSE_SHORT</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>1.56136</v>
+      </c>
+      <c r="E504" t="n">
+        <v>1.56104</v>
+      </c>
+      <c r="F504" t="n">
+        <v>1.56122</v>
+      </c>
+      <c r="G504" t="n">
+        <v>6</v>
+      </c>
+      <c r="H504" t="n">
+        <v>9</v>
+      </c>
+      <c r="I504" t="n">
+        <v>18</v>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>Ордер SHORT снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:09</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>1.56136</v>
+      </c>
+      <c r="E505" t="n">
+        <v>1.56104</v>
+      </c>
+      <c r="F505" t="n">
+        <v>1.56122</v>
+      </c>
+      <c r="G505" t="n">
+        <v>6</v>
+      </c>
+      <c r="H505" t="n">
+        <v>9</v>
+      </c>
+      <c r="I505" t="n">
+        <v>18</v>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:10</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>1.85428</v>
+      </c>
+      <c r="E506" t="n">
+        <v>1.85365</v>
+      </c>
+      <c r="F506" t="n">
+        <v>1.85311</v>
+      </c>
+      <c r="G506" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H506" t="n">
+        <v>52</v>
+      </c>
+      <c r="I506" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:10</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>3362.82</v>
+      </c>
+      <c r="E507" t="n">
+        <v>3367.56</v>
+      </c>
+      <c r="F507" t="n">
+        <v>3372.54</v>
+      </c>
+      <c r="G507" t="n">
+        <v>11</v>
+      </c>
+      <c r="H507" t="n">
+        <v>308</v>
+      </c>
+      <c r="I507" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:11</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>194.184</v>
+      </c>
+      <c r="E508" t="n">
+        <v>193.94</v>
+      </c>
+      <c r="F508" t="n">
+        <v>193.609</v>
+      </c>
+      <c r="G508" t="n">
+        <v>-29</v>
+      </c>
+      <c r="H508" t="n">
+        <v>161</v>
+      </c>
+      <c r="I508" t="n">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:11</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>34.4276</v>
+      </c>
+      <c r="E509" t="n">
+        <v>34.4608</v>
+      </c>
+      <c r="F509" t="n">
+        <v>34.4827</v>
+      </c>
+      <c r="G509" t="n">
+        <v>5</v>
+      </c>
+      <c r="H509" t="n">
+        <v>193</v>
+      </c>
+      <c r="I509" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:12</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>1.28765</v>
+      </c>
+      <c r="E510" t="n">
+        <v>1.28684</v>
+      </c>
+      <c r="F510" t="n">
+        <v>1.28592</v>
+      </c>
+      <c r="G510" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H510" t="n">
+        <v>11</v>
+      </c>
+      <c r="I510" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2025-06-05 03:06:13</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>1.28765</v>
+      </c>
+      <c r="E511" t="n">
+        <v>1.28684</v>
+      </c>
+      <c r="F511" t="n">
+        <v>1.28592</v>
+      </c>
+      <c r="G511" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H511" t="n">
+        <v>11</v>
+      </c>
+      <c r="I511" t="n">
+        <v>92</v>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:14</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>1.14023</v>
+      </c>
+      <c r="E512" t="n">
+        <v>1.1411</v>
+      </c>
+      <c r="F512" t="n">
+        <v>1.14202</v>
+      </c>
+      <c r="G512" t="n">
+        <v>27</v>
+      </c>
+      <c r="H512" t="n">
+        <v>135</v>
+      </c>
+      <c r="I512" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:14</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>0.60167</v>
+      </c>
+      <c r="E513" t="n">
+        <v>0.60228</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0.60271</v>
+      </c>
+      <c r="G513" t="n">
+        <v>5</v>
+      </c>
+      <c r="H513" t="n">
+        <v>134</v>
+      </c>
+      <c r="I513" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:15</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>0.84199</v>
+      </c>
+      <c r="E514" t="n">
+        <v>0.84215</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0.84246</v>
+      </c>
+      <c r="G514" t="n">
+        <v>9</v>
+      </c>
+      <c r="H514" t="n">
+        <v>31</v>
+      </c>
+      <c r="I514" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:15</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>0.82046</v>
+      </c>
+      <c r="E515" t="n">
+        <v>0.81934</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0.8182199999999999</v>
+      </c>
+      <c r="G515" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H515" t="n">
+        <v>112</v>
+      </c>
+      <c r="I515" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:15</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>143.374</v>
+      </c>
+      <c r="E516" t="n">
+        <v>143.101</v>
+      </c>
+      <c r="F516" t="n">
+        <v>142.824</v>
+      </c>
+      <c r="G516" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H516" t="n">
+        <v>257</v>
+      </c>
+      <c r="I516" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:16</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>0.93563</v>
+      </c>
+      <c r="E517" t="n">
+        <v>0.9351</v>
+      </c>
+      <c r="F517" t="n">
+        <v>0.9346100000000001</v>
+      </c>
+      <c r="G517" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H517" t="n">
+        <v>22</v>
+      </c>
+      <c r="I517" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:16</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>1.35399</v>
+      </c>
+      <c r="E518" t="n">
+        <v>1.35474</v>
+      </c>
+      <c r="F518" t="n">
+        <v>1.35532</v>
+      </c>
+      <c r="G518" t="n">
+        <v>13</v>
+      </c>
+      <c r="H518" t="n">
+        <v>109</v>
+      </c>
+      <c r="I518" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:18</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>1.35399</v>
+      </c>
+      <c r="E519" t="n">
+        <v>1.35474</v>
+      </c>
+      <c r="F519" t="n">
+        <v>1.35532</v>
+      </c>
+      <c r="G519" t="n">
+        <v>13</v>
+      </c>
+      <c r="H519" t="n">
+        <v>109</v>
+      </c>
+      <c r="I519" t="n">
+        <v>58</v>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:18</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>1.36938</v>
+      </c>
+      <c r="E520" t="n">
+        <v>1.36824</v>
+      </c>
+      <c r="F520" t="n">
+        <v>1.3675</v>
+      </c>
+      <c r="G520" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H520" t="n">
+        <v>43</v>
+      </c>
+      <c r="I520" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:20</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>1.36938</v>
+      </c>
+      <c r="E521" t="n">
+        <v>1.36824</v>
+      </c>
+      <c r="F521" t="n">
+        <v>1.3675</v>
+      </c>
+      <c r="G521" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H521" t="n">
+        <v>43</v>
+      </c>
+      <c r="I521" t="n">
+        <v>74</v>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:20</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>163.486</v>
+      </c>
+      <c r="E522" t="n">
+        <v>163.302</v>
+      </c>
+      <c r="F522" t="n">
+        <v>163.125</v>
+      </c>
+      <c r="G522" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H522" t="n">
+        <v>87</v>
+      </c>
+      <c r="I522" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:21</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>0.88761</v>
+      </c>
+      <c r="E523" t="n">
+        <v>0.88773</v>
+      </c>
+      <c r="F523" t="n">
+        <v>0.88808</v>
+      </c>
+      <c r="G523" t="n">
+        <v>27</v>
+      </c>
+      <c r="H523" t="n">
+        <v>144</v>
+      </c>
+      <c r="I523" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:21</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>0.6480900000000001</v>
+      </c>
+      <c r="E524" t="n">
+        <v>0.64875</v>
+      </c>
+      <c r="F524" t="n">
+        <v>0.64916</v>
+      </c>
+      <c r="G524" t="n">
+        <v>7</v>
+      </c>
+      <c r="H524" t="n">
+        <v>151</v>
+      </c>
+      <c r="I524" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:22</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>92.95699999999999</v>
+      </c>
+      <c r="E525" t="n">
+        <v>92.879</v>
+      </c>
+      <c r="F525" t="n">
+        <v>92.751</v>
+      </c>
+      <c r="G525" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H525" t="n">
+        <v>28</v>
+      </c>
+      <c r="I525" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:22</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>0.53179</v>
+      </c>
+      <c r="E526" t="n">
+        <v>0.53161</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0.53141</v>
+      </c>
+      <c r="G526" t="n">
+        <v>7</v>
+      </c>
+      <c r="H526" t="n">
+        <v>30</v>
+      </c>
+      <c r="I526" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:23</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>174.699</v>
+      </c>
+      <c r="E527" t="n">
+        <v>174.597</v>
+      </c>
+      <c r="F527" t="n">
+        <v>174.492</v>
+      </c>
+      <c r="G527" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H527" t="n">
+        <v>50</v>
+      </c>
+      <c r="I527" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:23</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>1.75875</v>
+      </c>
+      <c r="E528" t="n">
+        <v>1.75829</v>
+      </c>
+      <c r="F528" t="n">
+        <v>1.75801</v>
+      </c>
+      <c r="G528" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H528" t="n">
+        <v>132</v>
+      </c>
+      <c r="I528" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:25</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>CLOSE_LONG</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>1.75875</v>
+      </c>
+      <c r="E529" t="n">
+        <v>1.75829</v>
+      </c>
+      <c r="F529" t="n">
+        <v>1.75801</v>
+      </c>
+      <c r="G529" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H529" t="n">
+        <v>132</v>
+      </c>
+      <c r="I529" t="n">
+        <v>28</v>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>Ордер LONG снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:26</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>1.75875</v>
+      </c>
+      <c r="E530" t="n">
+        <v>1.75829</v>
+      </c>
+      <c r="F530" t="n">
+        <v>1.75801</v>
+      </c>
+      <c r="G530" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H530" t="n">
+        <v>132</v>
+      </c>
+      <c r="I530" t="n">
+        <v>28</v>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:26</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>1.1109</v>
+      </c>
+      <c r="E531" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F531" t="n">
+        <v>1.10897</v>
+      </c>
+      <c r="G531" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H531" t="n">
+        <v>53</v>
+      </c>
+      <c r="I531" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:27</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>1.56129</v>
+      </c>
+      <c r="E532" t="n">
+        <v>1.56111</v>
+      </c>
+      <c r="F532" t="n">
+        <v>1.56146</v>
+      </c>
+      <c r="G532" t="n">
+        <v>13</v>
+      </c>
+      <c r="H532" t="n">
+        <v>132</v>
+      </c>
+      <c r="I532" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:27</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>1.85419</v>
+      </c>
+      <c r="E533" t="n">
+        <v>1.85354</v>
+      </c>
+      <c r="F533" t="n">
+        <v>1.8531</v>
+      </c>
+      <c r="G533" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H533" t="n">
+        <v>100</v>
+      </c>
+      <c r="I533" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:28</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>3363.58</v>
+      </c>
+      <c r="E534" t="n">
+        <v>3368.52</v>
+      </c>
+      <c r="F534" t="n">
+        <v>3374.34</v>
+      </c>
+      <c r="G534" t="n">
+        <v>19</v>
+      </c>
+      <c r="H534" t="n">
+        <v>836</v>
+      </c>
+      <c r="I534" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:28</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>194.127</v>
+      </c>
+      <c r="E535" t="n">
+        <v>193.869</v>
+      </c>
+      <c r="F535" t="n">
+        <v>193.583</v>
+      </c>
+      <c r="G535" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H535" t="n">
+        <v>168</v>
+      </c>
+      <c r="I535" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:29</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>34.4326</v>
+      </c>
+      <c r="E536" t="n">
+        <v>34.4663</v>
+      </c>
+      <c r="F536" t="n">
+        <v>34.4934</v>
+      </c>
+      <c r="G536" t="n">
+        <v>10</v>
+      </c>
+      <c r="H536" t="n">
+        <v>596</v>
+      </c>
+      <c r="I536" t="n">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:06:29</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>1.28737</v>
+      </c>
+      <c r="E537" t="n">
+        <v>1.28652</v>
+      </c>
+      <c r="F537" t="n">
+        <v>1.28551</v>
+      </c>
+      <c r="G537" t="n">
+        <v>-25</v>
+      </c>
+      <c r="H537" t="n">
+        <v>131</v>
+      </c>
+      <c r="I537" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:30</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>1.14035</v>
+      </c>
+      <c r="E538" t="n">
+        <v>1.14124</v>
+      </c>
+      <c r="F538" t="n">
+        <v>1.14181</v>
+      </c>
+      <c r="G538" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H538" t="n">
+        <v>29</v>
+      </c>
+      <c r="I538" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:30</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>0.60182</v>
+      </c>
+      <c r="E539" t="n">
+        <v>0.60241</v>
+      </c>
+      <c r="F539" t="n">
+        <v>0.60292</v>
+      </c>
+      <c r="G539" t="n">
+        <v>5</v>
+      </c>
+      <c r="H539" t="n">
+        <v>9</v>
+      </c>
+      <c r="I539" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:31</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>0.8420299999999999</v>
+      </c>
+      <c r="E540" t="n">
+        <v>0.84222</v>
+      </c>
+      <c r="F540" t="n">
+        <v>0.84248</v>
+      </c>
+      <c r="G540" t="n">
+        <v>4</v>
+      </c>
+      <c r="H540" t="n">
+        <v>12</v>
+      </c>
+      <c r="I540" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:31</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>0.82029</v>
+      </c>
+      <c r="E541" t="n">
+        <v>0.81916</v>
+      </c>
+      <c r="F541" t="n">
+        <v>0.81839</v>
+      </c>
+      <c r="G541" t="n">
+        <v>5</v>
+      </c>
+      <c r="H541" t="n">
+        <v>12</v>
+      </c>
+      <c r="I541" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:32</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>143.328</v>
+      </c>
+      <c r="E542" t="n">
+        <v>143.053</v>
+      </c>
+      <c r="F542" t="n">
+        <v>142.856</v>
+      </c>
+      <c r="G542" t="n">
+        <v>5</v>
+      </c>
+      <c r="H542" t="n">
+        <v>13</v>
+      </c>
+      <c r="I542" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:33</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>0.93555</v>
+      </c>
+      <c r="E543" t="n">
+        <v>0.93502</v>
+      </c>
+      <c r="F543" t="n">
+        <v>0.93462</v>
+      </c>
+      <c r="G543" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H543" t="n">
+        <v>15</v>
+      </c>
+      <c r="I543" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:33</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>1.35406</v>
+      </c>
+      <c r="E544" t="n">
+        <v>1.35479</v>
+      </c>
+      <c r="F544" t="n">
+        <v>1.35505</v>
+      </c>
+      <c r="G544" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H544" t="n">
+        <v>45</v>
+      </c>
+      <c r="I544" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:33</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>1.36923</v>
+      </c>
+      <c r="E545" t="n">
+        <v>1.36815</v>
+      </c>
+      <c r="F545" t="n">
+        <v>1.36762</v>
+      </c>
+      <c r="G545" t="n">
+        <v>2</v>
+      </c>
+      <c r="H545" t="n">
+        <v>31</v>
+      </c>
+      <c r="I545" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:34</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>163.452</v>
+      </c>
+      <c r="E546" t="n">
+        <v>163.271</v>
+      </c>
+      <c r="F546" t="n">
+        <v>163.13</v>
+      </c>
+      <c r="G546" t="n">
+        <v>0</v>
+      </c>
+      <c r="H546" t="n">
+        <v>34</v>
+      </c>
+      <c r="I546" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:34</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>0.88761</v>
+      </c>
+      <c r="E547" t="n">
+        <v>0.88778</v>
+      </c>
+      <c r="F547" t="n">
+        <v>0.88817</v>
+      </c>
+      <c r="G547" t="n">
+        <v>13</v>
+      </c>
+      <c r="H547" t="n">
+        <v>51</v>
+      </c>
+      <c r="I547" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:35</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>0.64822</v>
+      </c>
+      <c r="E548" t="n">
+        <v>0.6488699999999999</v>
+      </c>
+      <c r="F548" t="n">
+        <v>0.64946</v>
+      </c>
+      <c r="G548" t="n">
+        <v>9</v>
+      </c>
+      <c r="H548" t="n">
+        <v>24</v>
+      </c>
+      <c r="I548" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:36</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>92.91</v>
+      </c>
+      <c r="E549" t="n">
+        <v>92.82899999999999</v>
+      </c>
+      <c r="F549" t="n">
+        <v>92.782</v>
+      </c>
+      <c r="G549" t="n">
+        <v>12</v>
+      </c>
+      <c r="H549" t="n">
+        <v>40</v>
+      </c>
+      <c r="I549" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:36</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>0.53174</v>
+      </c>
+      <c r="E550" t="n">
+        <v>0.53156</v>
+      </c>
+      <c r="F550" t="n">
+        <v>0.5315299999999999</v>
+      </c>
+      <c r="G550" t="n">
+        <v>13</v>
+      </c>
+      <c r="H550" t="n">
+        <v>26</v>
+      </c>
+      <c r="I550" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:38</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>CLOSE_SHORT</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>0.53174</v>
+      </c>
+      <c r="E551" t="n">
+        <v>0.53156</v>
+      </c>
+      <c r="F551" t="n">
+        <v>0.5315299999999999</v>
+      </c>
+      <c r="G551" t="n">
+        <v>13</v>
+      </c>
+      <c r="H551" t="n">
+        <v>26</v>
+      </c>
+      <c r="I551" t="n">
+        <v>3</v>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>Ордер SHORT снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:39</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>0.53174</v>
+      </c>
+      <c r="E552" t="n">
+        <v>0.53156</v>
+      </c>
+      <c r="F552" t="n">
+        <v>0.5315299999999999</v>
+      </c>
+      <c r="G552" t="n">
+        <v>13</v>
+      </c>
+      <c r="H552" t="n">
+        <v>26</v>
+      </c>
+      <c r="I552" t="n">
+        <v>3</v>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:39</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>174.676</v>
+      </c>
+      <c r="E553" t="n">
+        <v>174.576</v>
+      </c>
+      <c r="F553" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="G553" t="n">
+        <v>2</v>
+      </c>
+      <c r="H553" t="n">
+        <v>2</v>
+      </c>
+      <c r="I553" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:40</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>1.75874</v>
+      </c>
+      <c r="E554" t="n">
+        <v>1.7583</v>
+      </c>
+      <c r="F554" t="n">
+        <v>1.75769</v>
+      </c>
+      <c r="G554" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H554" t="n">
+        <v>97</v>
+      </c>
+      <c r="I554" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:40</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>1.11074</v>
+      </c>
+      <c r="E555" t="n">
+        <v>1.1098</v>
+      </c>
+      <c r="F555" t="n">
+        <v>1.10899</v>
+      </c>
+      <c r="G555" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H555" t="n">
+        <v>20</v>
+      </c>
+      <c r="I555" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:41</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>1.56129</v>
+      </c>
+      <c r="E556" t="n">
+        <v>1.56118</v>
+      </c>
+      <c r="F556" t="n">
+        <v>1.56129</v>
+      </c>
+      <c r="G556" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H556" t="n">
+        <v>3</v>
+      </c>
+      <c r="I556" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:41</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>1.85396</v>
+      </c>
+      <c r="E557" t="n">
+        <v>1.85341</v>
+      </c>
+      <c r="F557" t="n">
+        <v>1.85299</v>
+      </c>
+      <c r="G557" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H557" t="n">
+        <v>15</v>
+      </c>
+      <c r="I557" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:42</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>3364.25</v>
+      </c>
+      <c r="E558" t="n">
+        <v>3369.56</v>
+      </c>
+      <c r="F558" t="n">
+        <v>3373.48</v>
+      </c>
+      <c r="G558" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H558" t="n">
+        <v>54</v>
+      </c>
+      <c r="I558" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:43</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>194.077</v>
+      </c>
+      <c r="E559" t="n">
+        <v>193.813</v>
+      </c>
+      <c r="F559" t="n">
+        <v>193.588</v>
+      </c>
+      <c r="G559" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H559" t="n">
+        <v>48</v>
+      </c>
+      <c r="I559" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:43</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>34.4382</v>
+      </c>
+      <c r="E560" t="n">
+        <v>34.4712</v>
+      </c>
+      <c r="F560" t="n">
+        <v>34.4986</v>
+      </c>
+      <c r="G560" t="n">
+        <v>6</v>
+      </c>
+      <c r="H560" t="n">
+        <v>404</v>
+      </c>
+      <c r="I560" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2025-06-05 05:06:44</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>1.28721</v>
+      </c>
+      <c r="E561" t="n">
+        <v>1.28636</v>
+      </c>
+      <c r="F561" t="n">
+        <v>1.2856</v>
+      </c>
+      <c r="G561" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H561" t="n">
+        <v>16</v>
+      </c>
+      <c r="I561" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:44</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>1.1405</v>
+      </c>
+      <c r="E562" t="n">
+        <v>1.14137</v>
+      </c>
+      <c r="F562" t="n">
+        <v>1.14176</v>
+      </c>
+      <c r="G562" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H562" t="n">
+        <v>10</v>
+      </c>
+      <c r="I562" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:45</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>0.60182</v>
+      </c>
+      <c r="E563" t="n">
+        <v>0.60241</v>
+      </c>
+      <c r="F563" t="n">
+        <v>0.60292</v>
+      </c>
+      <c r="G563" t="n">
+        <v>5</v>
+      </c>
+      <c r="H563" t="n">
+        <v>81</v>
+      </c>
+      <c r="I563" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:45</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>0.8420800000000001</v>
+      </c>
+      <c r="E564" t="n">
+        <v>0.84228</v>
+      </c>
+      <c r="F564" t="n">
+        <v>0.8425</v>
+      </c>
+      <c r="G564" t="n">
+        <v>1</v>
+      </c>
+      <c r="H564" t="n">
+        <v>4</v>
+      </c>
+      <c r="I564" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:46</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>0.8201000000000001</v>
+      </c>
+      <c r="E565" t="n">
+        <v>0.81901</v>
+      </c>
+      <c r="F565" t="n">
+        <v>0.81839</v>
+      </c>
+      <c r="G565" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H565" t="n">
+        <v>11</v>
+      </c>
+      <c r="I565" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:46</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>143.277</v>
+      </c>
+      <c r="E566" t="n">
+        <v>143.016</v>
+      </c>
+      <c r="F566" t="n">
+        <v>142.852</v>
+      </c>
+      <c r="G566" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H566" t="n">
+        <v>34</v>
+      </c>
+      <c r="I566" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:47</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>0.93546</v>
+      </c>
+      <c r="E567" t="n">
+        <v>0.93496</v>
+      </c>
+      <c r="F567" t="n">
+        <v>0.93458</v>
+      </c>
+      <c r="G567" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H567" t="n">
+        <v>26</v>
+      </c>
+      <c r="I567" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:47</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>1.35416</v>
+      </c>
+      <c r="E568" t="n">
+        <v>1.35485</v>
+      </c>
+      <c r="F568" t="n">
+        <v>1.35497</v>
+      </c>
+      <c r="G568" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H568" t="n">
+        <v>2</v>
+      </c>
+      <c r="I568" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:48</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>1.3691</v>
+      </c>
+      <c r="E569" t="n">
+        <v>1.36806</v>
+      </c>
+      <c r="F569" t="n">
+        <v>1.36765</v>
+      </c>
+      <c r="G569" t="n">
+        <v>0</v>
+      </c>
+      <c r="H569" t="n">
+        <v>13</v>
+      </c>
+      <c r="I569" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:48</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>163.416</v>
+      </c>
+      <c r="E570" t="n">
+        <v>163.249</v>
+      </c>
+      <c r="F570" t="n">
+        <v>163.117</v>
+      </c>
+      <c r="G570" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H570" t="n">
+        <v>62</v>
+      </c>
+      <c r="I570" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:49</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>0.88761</v>
+      </c>
+      <c r="E571" t="n">
+        <v>0.88792</v>
+      </c>
+      <c r="F571" t="n">
+        <v>0.88811</v>
+      </c>
+      <c r="G571" t="n">
+        <v>2</v>
+      </c>
+      <c r="H571" t="n">
+        <v>17</v>
+      </c>
+      <c r="I571" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:49</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>0.64822</v>
+      </c>
+      <c r="E572" t="n">
+        <v>0.6488699999999999</v>
+      </c>
+      <c r="F572" t="n">
+        <v>0.6494</v>
+      </c>
+      <c r="G572" t="n">
+        <v>2</v>
+      </c>
+      <c r="H572" t="n">
+        <v>9</v>
+      </c>
+      <c r="I572" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:50</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>92.91</v>
+      </c>
+      <c r="E573" t="n">
+        <v>92.82899999999999</v>
+      </c>
+      <c r="F573" t="n">
+        <v>92.776</v>
+      </c>
+      <c r="G573" t="n">
+        <v>8</v>
+      </c>
+      <c r="H573" t="n">
+        <v>22</v>
+      </c>
+      <c r="I573" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:50</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>0.53168</v>
+      </c>
+      <c r="E574" t="n">
+        <v>0.53159</v>
+      </c>
+      <c r="F574" t="n">
+        <v>0.53148</v>
+      </c>
+      <c r="G574" t="n">
+        <v>0</v>
+      </c>
+      <c r="H574" t="n">
+        <v>0</v>
+      </c>
+      <c r="I574" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:51</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>174.656</v>
+      </c>
+      <c r="E575" t="n">
+        <v>174.565</v>
+      </c>
+      <c r="F575" t="n">
+        <v>174.499</v>
+      </c>
+      <c r="G575" t="n">
+        <v>3</v>
+      </c>
+      <c r="H575" t="n">
+        <v>15</v>
+      </c>
+      <c r="I575" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:51</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>1.75878</v>
+      </c>
+      <c r="E576" t="n">
+        <v>1.75812</v>
+      </c>
+      <c r="F576" t="n">
+        <v>1.7578</v>
+      </c>
+      <c r="G576" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H576" t="n">
+        <v>20</v>
+      </c>
+      <c r="I576" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:52</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>1.11056</v>
+      </c>
+      <c r="E577" t="n">
+        <v>1.10967</v>
+      </c>
+      <c r="F577" t="n">
+        <v>1.10892</v>
+      </c>
+      <c r="G577" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H577" t="n">
+        <v>15</v>
+      </c>
+      <c r="I577" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:52</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>1.56131</v>
+      </c>
+      <c r="E578" t="n">
+        <v>1.56124</v>
+      </c>
+      <c r="F578" t="n">
+        <v>1.56126</v>
+      </c>
+      <c r="G578" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H578" t="n">
+        <v>5</v>
+      </c>
+      <c r="I578" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:53</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>1.85396</v>
+      </c>
+      <c r="E579" t="n">
+        <v>1.85341</v>
+      </c>
+      <c r="F579" t="n">
+        <v>1.85298</v>
+      </c>
+      <c r="G579" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H579" t="n">
+        <v>17</v>
+      </c>
+      <c r="I579" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:53</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>3365.1</v>
+      </c>
+      <c r="E580" t="n">
+        <v>3370.5</v>
+      </c>
+      <c r="F580" t="n">
+        <v>3372.7</v>
+      </c>
+      <c r="G580" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H580" t="n">
+        <v>98</v>
+      </c>
+      <c r="I580" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:54</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>194.023</v>
+      </c>
+      <c r="E581" t="n">
+        <v>193.775</v>
+      </c>
+      <c r="F581" t="n">
+        <v>193.571</v>
+      </c>
+      <c r="G581" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H581" t="n">
+        <v>59</v>
+      </c>
+      <c r="I581" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:54</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>34.4433</v>
+      </c>
+      <c r="E582" t="n">
+        <v>34.4787</v>
+      </c>
+      <c r="F582" t="n">
+        <v>34.5052</v>
+      </c>
+      <c r="G582" t="n">
+        <v>8</v>
+      </c>
+      <c r="H582" t="n">
+        <v>428</v>
+      </c>
+      <c r="I582" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2025-06-05 06:06:55</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>1.28721</v>
+      </c>
+      <c r="E583" t="n">
+        <v>1.28636</v>
+      </c>
+      <c r="F583" t="n">
+        <v>1.28569</v>
+      </c>
+      <c r="G583" t="n">
+        <v>5</v>
+      </c>
+      <c r="H583" t="n">
+        <v>44</v>
+      </c>
+      <c r="I583" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:06:56</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D584" t="n">
+        <v>1.14063</v>
+      </c>
+      <c r="E584" t="n">
+        <v>1.14138</v>
+      </c>
+      <c r="F584" t="n">
+        <v>1.14157</v>
+      </c>
+      <c r="G584" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H584" t="n">
+        <v>51</v>
+      </c>
+      <c r="I584" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:06:57</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>CLOSE_LONG</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D585" t="n">
+        <v>1.14063</v>
+      </c>
+      <c r="E585" t="n">
+        <v>1.14138</v>
+      </c>
+      <c r="F585" t="n">
+        <v>1.14157</v>
+      </c>
+      <c r="G585" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H585" t="n">
+        <v>51</v>
+      </c>
+      <c r="I585" t="n">
+        <v>19</v>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>Ордер LONG снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:06:59</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D586" t="n">
+        <v>1.14063</v>
+      </c>
+      <c r="E586" t="n">
+        <v>1.14138</v>
+      </c>
+      <c r="F586" t="n">
+        <v>1.14157</v>
+      </c>
+      <c r="G586" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H586" t="n">
+        <v>51</v>
+      </c>
+      <c r="I586" t="n">
+        <v>19</v>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:06:59</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>0.60189</v>
+      </c>
+      <c r="E587" t="n">
+        <v>0.60255</v>
+      </c>
+      <c r="F587" t="n">
+        <v>0.6031</v>
+      </c>
+      <c r="G587" t="n">
+        <v>17</v>
+      </c>
+      <c r="H587" t="n">
+        <v>25</v>
+      </c>
+      <c r="I587" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:00</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>0.84213</v>
+      </c>
+      <c r="E588" t="n">
+        <v>0.84233</v>
+      </c>
+      <c r="F588" t="n">
+        <v>0.8424199999999999</v>
+      </c>
+      <c r="G588" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H588" t="n">
+        <v>13</v>
+      </c>
+      <c r="I588" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:00</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>0.81994</v>
+      </c>
+      <c r="E589" t="n">
+        <v>0.81897</v>
+      </c>
+      <c r="F589" t="n">
+        <v>0.8186099999999999</v>
+      </c>
+      <c r="G589" t="n">
+        <v>13</v>
+      </c>
+      <c r="H589" t="n">
+        <v>43</v>
+      </c>
+      <c r="I589" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:01</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>143.234</v>
+      </c>
+      <c r="E590" t="n">
+        <v>143</v>
+      </c>
+      <c r="F590" t="n">
+        <v>142.882</v>
+      </c>
+      <c r="G590" t="n">
+        <v>12</v>
+      </c>
+      <c r="H590" t="n">
+        <v>66</v>
+      </c>
+      <c r="I590" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:01</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>0.93538</v>
+      </c>
+      <c r="E591" t="n">
+        <v>0.93491</v>
+      </c>
+      <c r="F591" t="n">
+        <v>0.93465</v>
+      </c>
+      <c r="G591" t="n">
+        <v>3</v>
+      </c>
+      <c r="H591" t="n">
+        <v>12</v>
+      </c>
+      <c r="I591" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:02</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>1.35423</v>
+      </c>
+      <c r="E592" t="n">
+        <v>1.3548</v>
+      </c>
+      <c r="F592" t="n">
+        <v>1.35493</v>
+      </c>
+      <c r="G592" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H592" t="n">
+        <v>23</v>
+      </c>
+      <c r="I592" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:03</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>1.36898</v>
+      </c>
+      <c r="E593" t="n">
+        <v>1.36804</v>
+      </c>
+      <c r="F593" t="n">
+        <v>1.36775</v>
+      </c>
+      <c r="G593" t="n">
+        <v>5</v>
+      </c>
+      <c r="H593" t="n">
+        <v>23</v>
+      </c>
+      <c r="I593" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:03</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>163.387</v>
+      </c>
+      <c r="E594" t="n">
+        <v>163.229</v>
+      </c>
+      <c r="F594" t="n">
+        <v>163.122</v>
+      </c>
+      <c r="G594" t="n">
+        <v>4</v>
+      </c>
+      <c r="H594" t="n">
+        <v>7</v>
+      </c>
+      <c r="I594" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:04</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>0.88766</v>
+      </c>
+      <c r="E595" t="n">
+        <v>0.88797</v>
+      </c>
+      <c r="F595" t="n">
+        <v>0.88791</v>
+      </c>
+      <c r="G595" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H595" t="n">
+        <v>44</v>
+      </c>
+      <c r="I595" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:05</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>CLOSE_LONG</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>0.88766</v>
+      </c>
+      <c r="E596" t="n">
+        <v>0.88797</v>
+      </c>
+      <c r="F596" t="n">
+        <v>0.88791</v>
+      </c>
+      <c r="G596" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H596" t="n">
+        <v>44</v>
+      </c>
+      <c r="I596" t="n">
+        <v>6</v>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>Ордер LONG снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:07</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D597" t="n">
+        <v>0.88766</v>
+      </c>
+      <c r="E597" t="n">
+        <v>0.88797</v>
+      </c>
+      <c r="F597" t="n">
+        <v>0.88791</v>
+      </c>
+      <c r="G597" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H597" t="n">
+        <v>44</v>
+      </c>
+      <c r="I597" t="n">
+        <v>6</v>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:07</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>0.64829</v>
+      </c>
+      <c r="E598" t="n">
+        <v>0.64904</v>
+      </c>
+      <c r="F598" t="n">
+        <v>0.6494</v>
+      </c>
+      <c r="G598" t="n">
+        <v>2</v>
+      </c>
+      <c r="H598" t="n">
+        <v>64</v>
+      </c>
+      <c r="I598" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:08</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>92.887</v>
+      </c>
+      <c r="E599" t="n">
+        <v>92.827</v>
+      </c>
+      <c r="F599" t="n">
+        <v>92.771</v>
+      </c>
+      <c r="G599" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H599" t="n">
+        <v>38</v>
+      </c>
+      <c r="I599" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:08</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>0.53165</v>
+      </c>
+      <c r="E600" t="n">
+        <v>0.5316</v>
+      </c>
+      <c r="F600" t="n">
+        <v>0.53145</v>
+      </c>
+      <c r="G600" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H600" t="n">
+        <v>12</v>
+      </c>
+      <c r="I600" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:09</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>174.639</v>
+      </c>
+      <c r="E601" t="n">
+        <v>174.555</v>
+      </c>
+      <c r="F601" t="n">
+        <v>174.491</v>
+      </c>
+      <c r="G601" t="n">
+        <v>3</v>
+      </c>
+      <c r="H601" t="n">
+        <v>3</v>
+      </c>
+      <c r="I601" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:09</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>1.75875</v>
+      </c>
+      <c r="E602" t="n">
+        <v>1.75803</v>
+      </c>
+      <c r="F602" t="n">
+        <v>1.75809</v>
+      </c>
+      <c r="G602" t="n">
+        <v>8</v>
+      </c>
+      <c r="H602" t="n">
+        <v>61</v>
+      </c>
+      <c r="I602" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:11</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>CLOSE_SHORT</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>1.75875</v>
+      </c>
+      <c r="E603" t="n">
+        <v>1.75803</v>
+      </c>
+      <c r="F603" t="n">
+        <v>1.75809</v>
+      </c>
+      <c r="G603" t="n">
+        <v>8</v>
+      </c>
+      <c r="H603" t="n">
+        <v>61</v>
+      </c>
+      <c r="I603" t="n">
+        <v>6</v>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>Ордер SHORT снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:12</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>1.75875</v>
+      </c>
+      <c r="E604" t="n">
+        <v>1.75803</v>
+      </c>
+      <c r="F604" t="n">
+        <v>1.75809</v>
+      </c>
+      <c r="G604" t="n">
+        <v>8</v>
+      </c>
+      <c r="H604" t="n">
+        <v>61</v>
+      </c>
+      <c r="I604" t="n">
+        <v>6</v>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:13</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D605" t="n">
+        <v>1.1104</v>
+      </c>
+      <c r="E605" t="n">
+        <v>1.10956</v>
+      </c>
+      <c r="F605" t="n">
+        <v>1.10912</v>
+      </c>
+      <c r="G605" t="n">
+        <v>8</v>
+      </c>
+      <c r="H605" t="n">
+        <v>35</v>
+      </c>
+      <c r="I605" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:13</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>1.56134</v>
+      </c>
+      <c r="E606" t="n">
+        <v>1.56123</v>
+      </c>
+      <c r="F606" t="n">
+        <v>1.56115</v>
+      </c>
+      <c r="G606" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H606" t="n">
+        <v>31</v>
+      </c>
+      <c r="I606" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:14</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>1.85389</v>
+      </c>
+      <c r="E607" t="n">
+        <v>1.85337</v>
+      </c>
+      <c r="F607" t="n">
+        <v>1.853</v>
+      </c>
+      <c r="G607" t="n">
+        <v>1</v>
+      </c>
+      <c r="H607" t="n">
+        <v>5</v>
+      </c>
+      <c r="I607" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:15</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>3366</v>
+      </c>
+      <c r="E608" t="n">
+        <v>3370.63</v>
+      </c>
+      <c r="F608" t="n">
+        <v>3372.4</v>
+      </c>
+      <c r="G608" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H608" t="n">
+        <v>229</v>
+      </c>
+      <c r="I608" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:15</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>193.976</v>
+      </c>
+      <c r="E609" t="n">
+        <v>193.742</v>
+      </c>
+      <c r="F609" t="n">
+        <v>193.601</v>
+      </c>
+      <c r="G609" t="n">
+        <v>11</v>
+      </c>
+      <c r="H609" t="n">
+        <v>51</v>
+      </c>
+      <c r="I609" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:16</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D610" t="n">
+        <v>34.4481</v>
+      </c>
+      <c r="E610" t="n">
+        <v>34.4831</v>
+      </c>
+      <c r="F610" t="n">
+        <v>34.5038</v>
+      </c>
+      <c r="G610" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H610" t="n">
+        <v>47</v>
+      </c>
+      <c r="I610" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2025-06-05 07:07:16</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>1.28709</v>
+      </c>
+      <c r="E611" t="n">
+        <v>1.28617</v>
+      </c>
+      <c r="F611" t="n">
+        <v>1.28578</v>
+      </c>
+      <c r="G611" t="n">
+        <v>8</v>
+      </c>
+      <c r="H611" t="n">
+        <v>106</v>
+      </c>
+      <c r="I611" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2025-06-05 08:07:17</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>1.14076</v>
+      </c>
+      <c r="E612" t="n">
+        <v>1.1414</v>
+      </c>
+      <c r="F612" t="n">
+        <v>1.14148</v>
+      </c>
+      <c r="G612" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H612" t="n">
+        <v>55</v>
+      </c>
+      <c r="I612" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2025-06-05 08:07:17</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>0.60197</v>
+      </c>
+      <c r="E613" t="n">
+        <v>0.60262</v>
+      </c>
+      <c r="F613" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="G613" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H613" t="n">
+        <v>13</v>
+      </c>
+      <c r="I613" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2025-06-05 08:07:18</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>0.84217</v>
+      </c>
+      <c r="E614" t="n">
+        <v>0.84233</v>
+      </c>
+      <c r="F614" t="n">
+        <v>0.84239</v>
+      </c>
+      <c r="G614" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H614" t="n">
+        <v>8</v>
+      </c>
+      <c r="I614" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2025-06-05 08:07:18</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>0.81978</v>
+      </c>
+      <c r="E615" t="n">
+        <v>0.81894</v>
+      </c>
+      <c r="F615" t="n">
+        <v>0.81865</v>
+      </c>
+      <c r="G615" t="n">
+        <v>8</v>
+      </c>
+      <c r="H615" t="n">
+        <v>36</v>
+      </c>
+      <c r="I615" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2025-06-05 08:07:19</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>143.197</v>
+      </c>
+      <c r="E616" t="n">
+        <v>142.982</v>
+      </c>
+      <c r="F616" t="n">
+        <v>142.911</v>
+      </c>
+      <c r="G616" t="n">
+        <v>14</v>
+      </c>
+      <c r="H616" t="n">
+        <v>129</v>
+      </c>
+      <c r="I616" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2025-06-05 08:07:20</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>0.93532</v>
+      </c>
+      <c r="E617" t="n">
+        <v>0.93488</v>
+      </c>
+      <c r="F617" t="n">
+        <v>0.9346100000000001</v>
+      </c>
+      <c r="G617" t="n">
+        <v>0</v>
+      </c>
+      <c r="H617" t="n">
+        <v>6</v>
+      </c>
+      <c r="I617" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2025-06-05 08:07:20</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>1.35432</v>
+      </c>
+      <c r="E618" t="n">
+        <v>1.35485</v>
+      </c>
+      <c r="F618" t="n">
+        <v>1.35486</v>
+      </c>
+      <c r="G618" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H618" t="n">
+        <v>52</v>
+      </c>
+      <c r="I618" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:41:43</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>CLOSE_SHORT</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D619" t="n">
+        <v>1.14121</v>
+      </c>
+      <c r="E619" t="n">
+        <v>1.14223</v>
+      </c>
+      <c r="F619" t="n">
+        <v>1.14381</v>
+      </c>
+      <c r="G619" t="n">
+        <v>29</v>
+      </c>
+      <c r="H619" t="n">
+        <v>72</v>
+      </c>
+      <c r="I619" t="n">
+        <v>158</v>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>Ордер SHORT снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:41:45</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>1.14121</v>
+      </c>
+      <c r="E620" t="n">
+        <v>1.14223</v>
+      </c>
+      <c r="F620" t="n">
+        <v>1.14381</v>
+      </c>
+      <c r="G620" t="n">
+        <v>29</v>
+      </c>
+      <c r="H620" t="n">
+        <v>72</v>
+      </c>
+      <c r="I620" t="n">
+        <v>158</v>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:41:46</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>CLOSE_SHORT</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>0.81955</v>
+      </c>
+      <c r="E621" t="n">
+        <v>0.81932</v>
+      </c>
+      <c r="F621" t="n">
+        <v>0.81935</v>
+      </c>
+      <c r="G621" t="n">
+        <v>15</v>
+      </c>
+      <c r="H621" t="n">
+        <v>120</v>
+      </c>
+      <c r="I621" t="n">
+        <v>3</v>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>Ордер SHORT снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:41:48</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>0.81955</v>
+      </c>
+      <c r="E622" t="n">
+        <v>0.81932</v>
+      </c>
+      <c r="F622" t="n">
+        <v>0.81935</v>
+      </c>
+      <c r="G622" t="n">
+        <v>15</v>
+      </c>
+      <c r="H622" t="n">
+        <v>120</v>
+      </c>
+      <c r="I622" t="n">
+        <v>3</v>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:41:50</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>143.156</v>
+      </c>
+      <c r="E623" t="n">
+        <v>143.13</v>
+      </c>
+      <c r="F623" t="n">
+        <v>143.273</v>
+      </c>
+      <c r="G623" t="n">
+        <v>38</v>
+      </c>
+      <c r="H623" t="n">
+        <v>537</v>
+      </c>
+      <c r="I623" t="n">
+        <v>143</v>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:41:51</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>0.9354</v>
+      </c>
+      <c r="E624" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="F624" t="n">
+        <v>0.93731</v>
+      </c>
+      <c r="G624" t="n">
+        <v>39</v>
+      </c>
+      <c r="H624" t="n">
+        <v>193</v>
+      </c>
+      <c r="I624" t="n">
+        <v>131</v>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:41:53</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>1.35522</v>
+      </c>
+      <c r="E625" t="n">
+        <v>1.35645</v>
+      </c>
+      <c r="F625" t="n">
+        <v>1.35788</v>
+      </c>
+      <c r="G625" t="n">
+        <v>17</v>
+      </c>
+      <c r="H625" t="n">
+        <v>75</v>
+      </c>
+      <c r="I625" t="n">
+        <v>143</v>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:41:55</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>163.383</v>
+      </c>
+      <c r="E626" t="n">
+        <v>163.51</v>
+      </c>
+      <c r="F626" t="n">
+        <v>163.903</v>
+      </c>
+      <c r="G626" t="n">
+        <v>47</v>
+      </c>
+      <c r="H626" t="n">
+        <v>691</v>
+      </c>
+      <c r="I626" t="n">
+        <v>393</v>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:41:56</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>CLOSE_SHORT</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>0.8881</v>
+      </c>
+      <c r="E627" t="n">
+        <v>0.88871</v>
+      </c>
+      <c r="F627" t="n">
+        <v>0.88945</v>
+      </c>
+      <c r="G627" t="n">
+        <v>19</v>
+      </c>
+      <c r="H627" t="n">
+        <v>59</v>
+      </c>
+      <c r="I627" t="n">
+        <v>74</v>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>Ордер SHORT снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:41:58</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>0.8881</v>
+      </c>
+      <c r="E628" t="n">
+        <v>0.88871</v>
+      </c>
+      <c r="F628" t="n">
+        <v>0.88945</v>
+      </c>
+      <c r="G628" t="n">
+        <v>19</v>
+      </c>
+      <c r="H628" t="n">
+        <v>59</v>
+      </c>
+      <c r="I628" t="n">
+        <v>74</v>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:42:00</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D629" t="n">
+        <v>92.962</v>
+      </c>
+      <c r="E629" t="n">
+        <v>93.084</v>
+      </c>
+      <c r="F629" t="n">
+        <v>93.31699999999999</v>
+      </c>
+      <c r="G629" t="n">
+        <v>49</v>
+      </c>
+      <c r="H629" t="n">
+        <v>370</v>
+      </c>
+      <c r="I629" t="n">
+        <v>233</v>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:42:02</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D630" t="n">
+        <v>0.5321900000000001</v>
+      </c>
+      <c r="E630" t="n">
+        <v>0.53284</v>
+      </c>
+      <c r="F630" t="n">
+        <v>0.53367</v>
+      </c>
+      <c r="G630" t="n">
+        <v>30</v>
+      </c>
+      <c r="H630" t="n">
+        <v>95</v>
+      </c>
+      <c r="I630" t="n">
+        <v>83</v>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:42:03</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D631" t="n">
+        <v>174.632</v>
+      </c>
+      <c r="E631" t="n">
+        <v>174.655</v>
+      </c>
+      <c r="F631" t="n">
+        <v>174.822</v>
+      </c>
+      <c r="G631" t="n">
+        <v>33</v>
+      </c>
+      <c r="H631" t="n">
+        <v>390</v>
+      </c>
+      <c r="I631" t="n">
+        <v>167</v>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:42:05</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D632" t="n">
+        <v>1.11068</v>
+      </c>
+      <c r="E632" t="n">
+        <v>1.11135</v>
+      </c>
+      <c r="F632" t="n">
+        <v>1.11254</v>
+      </c>
+      <c r="G632" t="n">
+        <v>33</v>
+      </c>
+      <c r="H632" t="n">
+        <v>234</v>
+      </c>
+      <c r="I632" t="n">
+        <v>119</v>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:42:07</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D633" t="n">
+        <v>1.56063</v>
+      </c>
+      <c r="E633" t="n">
+        <v>1.56071</v>
+      </c>
+      <c r="F633" t="n">
+        <v>1.56187</v>
+      </c>
+      <c r="G633" t="n">
+        <v>14</v>
+      </c>
+      <c r="H633" t="n">
+        <v>150</v>
+      </c>
+      <c r="I633" t="n">
+        <v>116</v>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:42:09</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>CLOSE_SHORT</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D634" t="n">
+        <v>1.85337</v>
+      </c>
+      <c r="E634" t="n">
+        <v>1.85351</v>
+      </c>
+      <c r="F634" t="n">
+        <v>1.85423</v>
+      </c>
+      <c r="G634" t="n">
+        <v>15</v>
+      </c>
+      <c r="H634" t="n">
+        <v>178</v>
+      </c>
+      <c r="I634" t="n">
+        <v>72</v>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>Ордер SHORT снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:42:10</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D635" t="n">
+        <v>1.85337</v>
+      </c>
+      <c r="E635" t="n">
+        <v>1.85351</v>
+      </c>
+      <c r="F635" t="n">
+        <v>1.85423</v>
+      </c>
+      <c r="G635" t="n">
+        <v>15</v>
+      </c>
+      <c r="H635" t="n">
+        <v>178</v>
+      </c>
+      <c r="I635" t="n">
+        <v>72</v>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:42:12</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D636" t="n">
+        <v>3373.13</v>
+      </c>
+      <c r="E636" t="n">
+        <v>3378.84</v>
+      </c>
+      <c r="F636" t="n">
+        <v>3376.51</v>
+      </c>
+      <c r="G636" t="n">
+        <v>-38</v>
+      </c>
+      <c r="H636" t="n">
+        <v>2695</v>
+      </c>
+      <c r="I636" t="n">
+        <v>233</v>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2025-06-05 18:42:14</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>194.016</v>
+      </c>
+      <c r="E637" t="n">
+        <v>194.154</v>
+      </c>
+      <c r="F637" t="n">
+        <v>194.544</v>
+      </c>
+      <c r="G637" t="n">
+        <v>59</v>
+      </c>
+      <c r="H637" t="n">
+        <v>846</v>
+      </c>
+      <c r="I637" t="n">
+        <v>390</v>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2025-06-05 19:00:53</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>CLOSE_LONG</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>1.7569</v>
+      </c>
+      <c r="E638" t="n">
+        <v>1.75624</v>
+      </c>
+      <c r="F638" t="n">
+        <v>1.75572</v>
+      </c>
+      <c r="G638" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H638" t="n">
+        <v>31</v>
+      </c>
+      <c r="I638" t="n">
+        <v>52</v>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>Ордер LONG снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2025-06-05 19:00:55</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>1.7569</v>
+      </c>
+      <c r="E639" t="n">
+        <v>1.75624</v>
+      </c>
+      <c r="F639" t="n">
+        <v>1.75572</v>
+      </c>
+      <c r="G639" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H639" t="n">
+        <v>31</v>
+      </c>
+      <c r="I639" t="n">
+        <v>52</v>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2025-06-05 19:00:57</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>CLOSE_LONG</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>34.8237</v>
+      </c>
+      <c r="E640" t="n">
+        <v>35.1995</v>
+      </c>
+      <c r="F640" t="n">
+        <v>35.4545</v>
+      </c>
+      <c r="G640" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H640" t="n">
+        <v>875</v>
+      </c>
+      <c r="I640" t="n">
+        <v>2550</v>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>Ордер LONG снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2025-06-05 19:00:58</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D641" t="n">
+        <v>34.8237</v>
+      </c>
+      <c r="E641" t="n">
+        <v>35.1995</v>
+      </c>
+      <c r="F641" t="n">
+        <v>35.4545</v>
+      </c>
+      <c r="G641" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H641" t="n">
+        <v>875</v>
+      </c>
+      <c r="I641" t="n">
+        <v>2550</v>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2025-06-05 19:01:00</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D642" t="n">
+        <v>1.28589</v>
+      </c>
+      <c r="E642" t="n">
+        <v>1.28486</v>
+      </c>
+      <c r="F642" t="n">
+        <v>1.28487</v>
+      </c>
+      <c r="G642" t="n">
+        <v>26</v>
+      </c>
+      <c r="H642" t="n">
+        <v>143</v>
+      </c>
+      <c r="I642" t="n">
+        <v>1</v>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:01</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>EURUSDrfd</t>
+        </is>
+      </c>
+      <c r="D643" t="n">
+        <v>1.14168</v>
+      </c>
+      <c r="E643" t="n">
+        <v>1.14303</v>
+      </c>
+      <c r="F643" t="n">
+        <v>1.14397</v>
+      </c>
+      <c r="G643" t="n">
+        <v>21</v>
+      </c>
+      <c r="H643" t="n">
+        <v>71</v>
+      </c>
+      <c r="I643" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:02</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>NZDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D644" t="n">
+        <v>0.60345</v>
+      </c>
+      <c r="E644" t="n">
+        <v>0.60437</v>
+      </c>
+      <c r="F644" t="n">
+        <v>0.60461</v>
+      </c>
+      <c r="G644" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H644" t="n">
+        <v>44</v>
+      </c>
+      <c r="I644" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:03</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>EURGBPrfd</t>
+        </is>
+      </c>
+      <c r="D645" t="n">
+        <v>0.8420299999999999</v>
+      </c>
+      <c r="E645" t="n">
+        <v>0.8421999999999999</v>
+      </c>
+      <c r="F645" t="n">
+        <v>0.84233</v>
+      </c>
+      <c r="G645" t="n">
+        <v>5</v>
+      </c>
+      <c r="H645" t="n">
+        <v>19</v>
+      </c>
+      <c r="I645" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:04</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>USDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D646" t="n">
+        <v>0.81953</v>
+      </c>
+      <c r="E646" t="n">
+        <v>0.81936</v>
+      </c>
+      <c r="F646" t="n">
+        <v>0.81947</v>
+      </c>
+      <c r="G646" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H646" t="n">
+        <v>27</v>
+      </c>
+      <c r="I646" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:04</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>USDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D647" t="n">
+        <v>143.165</v>
+      </c>
+      <c r="E647" t="n">
+        <v>143.218</v>
+      </c>
+      <c r="F647" t="n">
+        <v>143.405</v>
+      </c>
+      <c r="G647" t="n">
+        <v>14</v>
+      </c>
+      <c r="H647" t="n">
+        <v>127</v>
+      </c>
+      <c r="I647" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:05</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>EURCHFrfd</t>
+        </is>
+      </c>
+      <c r="D648" t="n">
+        <v>0.9357799999999999</v>
+      </c>
+      <c r="E648" t="n">
+        <v>0.93667</v>
+      </c>
+      <c r="F648" t="n">
+        <v>0.9376</v>
+      </c>
+      <c r="G648" t="n">
+        <v>6</v>
+      </c>
+      <c r="H648" t="n">
+        <v>24</v>
+      </c>
+      <c r="I648" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:05</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>GBPUSDrfd</t>
+        </is>
+      </c>
+      <c r="D649" t="n">
+        <v>1.35572</v>
+      </c>
+      <c r="E649" t="n">
+        <v>1.35707</v>
+      </c>
+      <c r="F649" t="n">
+        <v>1.35799</v>
+      </c>
+      <c r="G649" t="n">
+        <v>8</v>
+      </c>
+      <c r="H649" t="n">
+        <v>42</v>
+      </c>
+      <c r="I649" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:06</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>USDCADrfd</t>
+        </is>
+      </c>
+      <c r="D650" t="n">
+        <v>1.36731</v>
+      </c>
+      <c r="E650" t="n">
+        <v>1.36626</v>
+      </c>
+      <c r="F650" t="n">
+        <v>1.36611</v>
+      </c>
+      <c r="G650" t="n">
+        <v>7</v>
+      </c>
+      <c r="H650" t="n">
+        <v>61</v>
+      </c>
+      <c r="I650" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:07</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>EURJPYrfd</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>163.465</v>
+      </c>
+      <c r="E651" t="n">
+        <v>163.723</v>
+      </c>
+      <c r="F651" t="n">
+        <v>164.073</v>
+      </c>
+      <c r="G651" t="n">
+        <v>23</v>
+      </c>
+      <c r="H651" t="n">
+        <v>236</v>
+      </c>
+      <c r="I651" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:07</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>AUDCADrfd</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>0.8883799999999999</v>
+      </c>
+      <c r="E652" t="n">
+        <v>0.88905</v>
+      </c>
+      <c r="F652" t="n">
+        <v>0.88967</v>
+      </c>
+      <c r="G652" t="n">
+        <v>8</v>
+      </c>
+      <c r="H652" t="n">
+        <v>26</v>
+      </c>
+      <c r="I652" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:08</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>AUDUSDrfd</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>0.6495</v>
+      </c>
+      <c r="E653" t="n">
+        <v>0.65058</v>
+      </c>
+      <c r="F653" t="n">
+        <v>0.65128</v>
+      </c>
+      <c r="G653" t="n">
+        <v>3</v>
+      </c>
+      <c r="H653" t="n">
+        <v>8</v>
+      </c>
+      <c r="I653" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:08</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>AUDJPYrfd</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>93.02</v>
+      </c>
+      <c r="E654" t="n">
+        <v>93.199</v>
+      </c>
+      <c r="F654" t="n">
+        <v>93.395</v>
+      </c>
+      <c r="G654" t="n">
+        <v>14</v>
+      </c>
+      <c r="H654" t="n">
+        <v>76</v>
+      </c>
+      <c r="I654" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:09</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>AUDCHFrfd</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>0.53248</v>
+      </c>
+      <c r="E655" t="n">
+        <v>0.5332</v>
+      </c>
+      <c r="F655" t="n">
+        <v>0.53373</v>
+      </c>
+      <c r="G655" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H655" t="n">
+        <v>24</v>
+      </c>
+      <c r="I655" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:10</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>CHFJPYrfd</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>174.65</v>
+      </c>
+      <c r="E656" t="n">
+        <v>174.753</v>
+      </c>
+      <c r="F656" t="n">
+        <v>174.951</v>
+      </c>
+      <c r="G656" t="n">
+        <v>27</v>
+      </c>
+      <c r="H656" t="n">
+        <v>219</v>
+      </c>
+      <c r="I656" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:10</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D657" t="n">
+        <v>1.75682</v>
+      </c>
+      <c r="E657" t="n">
+        <v>1.75615</v>
+      </c>
+      <c r="F657" t="n">
+        <v>1.7562</v>
+      </c>
+      <c r="G657" t="n">
+        <v>20</v>
+      </c>
+      <c r="H657" t="n">
+        <v>135</v>
+      </c>
+      <c r="I657" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:12</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>CLOSE_SHORT</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>1.75682</v>
+      </c>
+      <c r="E658" t="n">
+        <v>1.75615</v>
+      </c>
+      <c r="F658" t="n">
+        <v>1.7562</v>
+      </c>
+      <c r="G658" t="n">
+        <v>20</v>
+      </c>
+      <c r="H658" t="n">
+        <v>135</v>
+      </c>
+      <c r="I658" t="n">
+        <v>5</v>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>Ордер SHORT снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:13</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>EURAUDrfd</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>1.75682</v>
+      </c>
+      <c r="E659" t="n">
+        <v>1.75615</v>
+      </c>
+      <c r="F659" t="n">
+        <v>1.7562</v>
+      </c>
+      <c r="G659" t="n">
+        <v>20</v>
+      </c>
+      <c r="H659" t="n">
+        <v>135</v>
+      </c>
+      <c r="I659" t="n">
+        <v>5</v>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:14</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>GBPCHFrfd</t>
+        </is>
+      </c>
+      <c r="D660" t="n">
+        <v>1.11105</v>
+      </c>
+      <c r="E660" t="n">
+        <v>1.1119</v>
+      </c>
+      <c r="F660" t="n">
+        <v>1.11282</v>
+      </c>
+      <c r="G660" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H660" t="n">
+        <v>3</v>
+      </c>
+      <c r="I660" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:15</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>EURCADrfd</t>
+        </is>
+      </c>
+      <c r="D661" t="n">
+        <v>1.56083</v>
+      </c>
+      <c r="E661" t="n">
+        <v>1.56145</v>
+      </c>
+      <c r="F661" t="n">
+        <v>1.56257</v>
+      </c>
+      <c r="G661" t="n">
+        <v>21</v>
+      </c>
+      <c r="H661" t="n">
+        <v>160</v>
+      </c>
+      <c r="I661" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:15</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>GBPCADrfd</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>1.85355</v>
+      </c>
+      <c r="E662" t="n">
+        <v>1.85393</v>
+      </c>
+      <c r="F662" t="n">
+        <v>1.85495</v>
+      </c>
+      <c r="G662" t="n">
+        <v>24</v>
+      </c>
+      <c r="H662" t="n">
+        <v>134</v>
+      </c>
+      <c r="I662" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:16</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>3374.74</v>
+      </c>
+      <c r="E663" t="n">
+        <v>3375.42</v>
+      </c>
+      <c r="F663" t="n">
+        <v>3366.71</v>
+      </c>
+      <c r="G663" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H663" t="n">
+        <v>1421</v>
+      </c>
+      <c r="I663" t="n">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:18</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>OPEN_SHORT</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>XAUUSDrfd</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>3374.74</v>
+      </c>
+      <c r="E664" t="n">
+        <v>3375.42</v>
+      </c>
+      <c r="F664" t="n">
+        <v>3366.71</v>
+      </c>
+      <c r="G664" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H664" t="n">
+        <v>1421</v>
+      </c>
+      <c r="I664" t="n">
+        <v>871</v>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>Ордер SHORT выставлен по условию</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:18</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>GBPJPYrfd</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>194.097</v>
+      </c>
+      <c r="E665" t="n">
+        <v>194.356</v>
+      </c>
+      <c r="F665" t="n">
+        <v>194.739</v>
+      </c>
+      <c r="G665" t="n">
+        <v>31</v>
+      </c>
+      <c r="H665" t="n">
+        <v>241</v>
+      </c>
+      <c r="I665" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:19</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>34.8983</v>
+      </c>
+      <c r="E666" t="n">
+        <v>35.2464</v>
+      </c>
+      <c r="F666" t="n">
+        <v>35.4915</v>
+      </c>
+      <c r="G666" t="n">
+        <v>19</v>
+      </c>
+      <c r="H666" t="n">
+        <v>685</v>
+      </c>
+      <c r="I666" t="n">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:20</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>CLOSE_SHORT</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>34.8983</v>
+      </c>
+      <c r="E667" t="n">
+        <v>35.2464</v>
+      </c>
+      <c r="F667" t="n">
+        <v>35.4915</v>
+      </c>
+      <c r="G667" t="n">
+        <v>19</v>
+      </c>
+      <c r="H667" t="n">
+        <v>685</v>
+      </c>
+      <c r="I667" t="n">
+        <v>2451</v>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>Ордер SHORT снят</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:22</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>OPEN_LONG</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>XAGUSDrfd</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>34.8983</v>
+      </c>
+      <c r="E668" t="n">
+        <v>35.2464</v>
+      </c>
+      <c r="F668" t="n">
+        <v>35.4915</v>
+      </c>
+      <c r="G668" t="n">
+        <v>19</v>
+      </c>
+      <c r="H668" t="n">
+        <v>685</v>
+      </c>
+      <c r="I668" t="n">
+        <v>2451</v>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>Ордер LONG выставлен по закрытию предыдущего</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2025-06-05 20:01:23</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>LOG</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>USDSGDrfd</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>1.28589</v>
+      </c>
+      <c r="E669" t="n">
+        <v>1.28486</v>
+      </c>
+      <c r="F669" t="n">
+        <v>1.28486</v>
+      </c>
+      <c r="G669" t="n">
+        <v>25</v>
+      </c>
+      <c r="H669" t="n">
+        <v>95</v>
+      </c>
+      <c r="I669" t="n">
+        <v>0</v>
+      </c>
+      <c r="J669" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
